--- a/7- Advance Excel/1-vlookup.xlsx
+++ b/7- Advance Excel/1-vlookup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a6ce4a7617f1ad9/Desktop/courses/Data Analytics/7- Advance Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_F25DC773A252ABDACC1048C8291E62A85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BFC3E0B-66EA-4AD7-8964-FA7F0D1387A3}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_F25DC773A252ABDACC1048C8291E62A85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1F4CD2B-97DB-4237-9E4D-465CA44093B0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -730,6 +730,11 @@
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{0000000B-0E3D-4A9B-B85C-7402D57F1391}"/>
+                    </c:ext>
+                  </c:extLst>
                 </c:dPt>
                 <c:dPt>
                   <c:idx val="1"/>
@@ -745,6 +750,11 @@
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{0000000D-0E3D-4A9B-B85C-7402D57F1391}"/>
+                    </c:ext>
+                  </c:extLst>
                 </c:dPt>
                 <c:dPt>
                   <c:idx val="2"/>
@@ -760,6 +770,11 @@
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{0000000F-0E3D-4A9B-B85C-7402D57F1391}"/>
+                    </c:ext>
+                  </c:extLst>
                 </c:dPt>
                 <c:dPt>
                   <c:idx val="3"/>
@@ -775,6 +790,11 @@
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{00000011-0E3D-4A9B-B85C-7402D57F1391}"/>
+                    </c:ext>
+                  </c:extLst>
                 </c:dPt>
                 <c:dPt>
                   <c:idx val="4"/>
@@ -790,6 +810,11 @@
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
+                  <c:extLst>
+                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                      <c16:uniqueId val="{00000013-0E3D-4A9B-B85C-7402D57F1391}"/>
+                    </c:ext>
+                  </c:extLst>
                 </c:dPt>
                 <c:dLbls>
                   <c:spPr>

--- a/7- Advance Excel/1-vlookup.xlsx
+++ b/7- Advance Excel/1-vlookup.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a6ce4a7617f1ad9/Desktop/courses/Data Analytics/7- Advance Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_F25DC773A252ABDACC1048C8291E62A85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1F4CD2B-97DB-4237-9E4D-465CA44093B0}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_F25DC773A252ABDACC1048C8291E62A85BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F764A32D-3309-48C3-BFC3-AA0D9E9B0C56}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="85">
   <si>
     <t>ProductID</t>
   </si>
@@ -225,6 +226,93 @@
   </si>
   <si>
     <t xml:space="preserve">Total  salary </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Students Reports  </t>
+  </si>
+  <si>
+    <t>RollNo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branch  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marks  </t>
+  </si>
+  <si>
+    <t>CSE</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Rohit Singh</t>
+  </si>
+  <si>
+    <t>Mechanical</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Neha Gupta</t>
+  </si>
+  <si>
+    <t>Arjun Yadav</t>
+  </si>
+  <si>
+    <t>Civil</t>
+  </si>
+  <si>
+    <t>Sneha Jain</t>
+  </si>
+  <si>
+    <t>Karan Mishra</t>
+  </si>
+  <si>
+    <t>Electrical</t>
+  </si>
+  <si>
+    <t>Pooja Thakur</t>
+  </si>
+  <si>
+    <t>Aditya Tiwari</t>
+  </si>
+  <si>
+    <t>Simran Khan</t>
+  </si>
+  <si>
+    <t>Vikash Patel</t>
+  </si>
+  <si>
+    <t>Anjali Sharma</t>
+  </si>
+  <si>
+    <t>Deepak Sahu</t>
+  </si>
+  <si>
+    <t>Riya Verma</t>
+  </si>
+  <si>
+    <t>Mohit Jain</t>
+  </si>
+  <si>
+    <t>Kavya Singh</t>
+  </si>
+  <si>
+    <t>Saurabh Gupta</t>
+  </si>
+  <si>
+    <t>Nisha Yadav</t>
+  </si>
+  <si>
+    <t>Harsh Patel</t>
   </si>
 </sst>
 </file>
@@ -280,10 +368,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2567,4 +2661,456 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52FBF4AF-8006-46C8-A636-6677D9DC911A}">
+  <dimension ref="A1:L22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.77734375" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" customWidth="1"/>
+    <col min="3" max="3" width="14.21875" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>101</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="4">
+        <v>85</v>
+      </c>
+      <c r="H3">
+        <v>101</v>
+      </c>
+      <c r="I3" t="str" cm="1">
+        <f t="array" ref="I3:L3">VLOOKUP(H3,$A$2:$E$22, {2,3,4,5})</f>
+        <v>Rahul Sharma</v>
+      </c>
+      <c r="J3" t="str">
+        <v>CSE</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="L3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>102</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="4">
+        <v>78</v>
+      </c>
+      <c r="H4">
+        <v>108</v>
+      </c>
+      <c r="I4" t="str" cm="1">
+        <f t="array" ref="I4:L4">VLOOKUP(H4,$A$2:$E$22, {2,3,4,5})</f>
+        <v>Karan Mishra</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Electrical</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="L4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>103</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="4">
+        <v>92</v>
+      </c>
+      <c r="H5">
+        <v>105</v>
+      </c>
+      <c r="I5" t="str" cm="1">
+        <f t="array" ref="I5:L5">VLOOKUP(H5,$A$2:$E$22, {2,3,4,5})</f>
+        <v>Neha Gupta</v>
+      </c>
+      <c r="J5" t="str">
+        <v>IT</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="L5">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>104</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="4">
+        <v>28</v>
+      </c>
+      <c r="H6">
+        <v>109</v>
+      </c>
+      <c r="I6" t="str" cm="1">
+        <f t="array" ref="I6:L6">VLOOKUP(H6,$A$2:$E$22, {2,3,4,5})</f>
+        <v>Pooja Thakur</v>
+      </c>
+      <c r="J6" t="str">
+        <v>IT</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="L6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>105</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>106</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="4">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>107</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>108</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>109</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>110</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>111</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>112</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>113</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>114</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>115</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>116</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="4">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>117</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
+        <v>118</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>119</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
+        <v>120</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="4">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>